--- a/BOM 자료/A11-D1-0000/A11-D1-0060_27형_288C_고객B 쿠웨이트향.xlsx
+++ b/BOM 자료/A11-D1-0000/A11-D1-0060_27형_288C_고객B 쿠웨이트향.xlsx
@@ -403,7 +403,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>회사명 : (주)샘플전자 / A11-D1-0060 / 광접속함체(SPFC-D1_288C_RIBBON) [LS, OFC-288C/288FO]</v>
+        <v>회사명 : (주)샘플전자 / A11-D1-0060 / 광기구(GKFC-D1_288C_RIBBON) [LS, OFC-288C/288FO]</v>
       </c>
       <c r="B1" t="str">
         <v/>
@@ -432,7 +432,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>SP-00001</v>
+        <v>GK-00001</v>
       </c>
       <c r="B2" t="str">
         <v>품목명</v>
@@ -461,10 +461,10 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>SP-00105</v>
+        <v>GK-00105</v>
       </c>
       <c r="B3" t="str">
-        <v>SPFC-D1 상판 (SPFC-D1 TOP)</v>
+        <v>GKFC-D1 상판 (GKFC-D1 TOP)</v>
       </c>
       <c r="C3" t="str">
         <v/>
@@ -490,10 +490,10 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>SP-00106</v>
+        <v>GK-00106</v>
       </c>
       <c r="B4" t="str">
-        <v>SPFC-D1 하판 (SPFC-D1 BOTTOM)</v>
+        <v>GKFC-D1 하판 (GKFC-D1 BOTTOM)</v>
       </c>
       <c r="C4" t="str">
         <v/>
@@ -519,7 +519,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>SP-00068</v>
+        <v>GK-00068</v>
       </c>
       <c r="B5" t="str">
         <v>OFC 광케이블 고정대 B형 (OFC OPTICAL CABLE FIXTURE B TYPE)</v>
@@ -548,7 +548,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>SP-00107</v>
+        <v>GK-00107</v>
       </c>
       <c r="B6" t="str">
         <v>OFC 광케이블 고정대 C형 (OFC OPTICAL CABLE FIXTURE C TYPE)</v>
@@ -577,10 +577,10 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>SP-00136</v>
+        <v>GK-00136</v>
       </c>
       <c r="B7" t="str">
-        <v>SPFC-C1/C2 힌지 CLOSE (SPFC-C1/C2 HINGE CLOSE)</v>
+        <v>GKFC-C1/C2 힌지 CLOSE (GKFC-C1/C2 HINGE CLOSE)</v>
       </c>
       <c r="C7" t="str">
         <v>Closed Type</v>
@@ -606,10 +606,10 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>SP-00137</v>
+        <v>GK-00137</v>
       </c>
       <c r="B8" t="str">
-        <v>SPFC-C1/C2 힌지 OPEN (SPFC-C1/C2 HINGE OPEN)</v>
+        <v>GKFC-C1/C2 힌지 OPEN (GKFC-C1/C2 HINGE OPEN)</v>
       </c>
       <c r="C8" t="str">
         <v>Opened Type</v>
@@ -635,10 +635,10 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>SP-00108</v>
+        <v>GK-00108</v>
       </c>
       <c r="B9" t="str">
-        <v>SPFC-D1 트레이 (SPFC-D1 TRAY)</v>
+        <v>GKFC-D1 트레이 (GKFC-D1 TRAY)</v>
       </c>
       <c r="C9" t="str">
         <v/>
@@ -664,7 +664,7 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>SP-00109</v>
+        <v>GK-00109</v>
       </c>
       <c r="B10" t="str">
         <v>트레이 OZ_리본용 12슬롯 (SPLICE HOLDER_RIBBON TYPE 12 SLOT)</v>
@@ -693,10 +693,10 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>SP-00111</v>
+        <v>GK-00111</v>
       </c>
       <c r="B11" t="str">
-        <v>SPFC 인입구 마개 OD15 (SPFC LEADING IN ROD OD15)</v>
+        <v>GKFC 인입구 마개 OD15 (GKFC LEADING IN ROD OD15)</v>
       </c>
       <c r="C11" t="str">
         <v>15mm</v>
@@ -722,10 +722,10 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>SP-00112</v>
+        <v>GK-00112</v>
       </c>
       <c r="B12" t="str">
-        <v>SPFC 인입구 마개 OD23 (SPFC LEADING IN ROD OD23)</v>
+        <v>GKFC 인입구 마개 OD23 (GKFC LEADING IN ROD OD23)</v>
       </c>
       <c r="C12" t="str">
         <v>23mm</v>
@@ -751,7 +751,7 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>SP-00069</v>
+        <v>GK-00069</v>
       </c>
       <c r="B13" t="str">
         <v>OFC 스패츌라 (OFC SPATULAR)</v>
@@ -780,7 +780,7 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>SP-00050</v>
+        <v>GK-00050</v>
       </c>
       <c r="B14" t="str">
         <v>압축 스프링 ID6.5*WD0.5*CL5*L35 (COMPRESSION SPRING ID6.5*WD0.5*CL5*L35)</v>
@@ -809,10 +809,10 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>SP-00113</v>
+        <v>GK-00113</v>
       </c>
       <c r="B15" t="str">
-        <v>SPFC-D1 접지바 (SPFC-D1 GROUND BAR)</v>
+        <v>GKFC-D1 접지바 (GKFC-D1 GROUND BAR)</v>
       </c>
       <c r="C15" t="str">
         <v/>
@@ -838,10 +838,10 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>SP-00114</v>
+        <v>GK-00114</v>
       </c>
       <c r="B16" t="str">
-        <v>SPFC-C1 인장선 고정철판 (SPFC-C1 TENSION LINE FIXTURE)</v>
+        <v>GKFC-C1 인장선 고정철판 (GKFC-C1 TENSION LINE FIXTURE)</v>
       </c>
       <c r="C16" t="str">
         <v>ㄷ자</v>
@@ -867,10 +867,10 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>SP-00115</v>
+        <v>GK-00115</v>
       </c>
       <c r="B17" t="str">
-        <v>SPFC-D1 트레이 스토퍼 (SPFC-D1 TRAY STOPPER)</v>
+        <v>GKFC-D1 트레이 스토퍼 (GKFC-D1 TRAY STOPPER)</v>
       </c>
       <c r="C17" t="str">
         <v/>
@@ -896,10 +896,10 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>SP-00064</v>
+        <v>GK-00064</v>
       </c>
       <c r="B18" t="str">
-        <v>SPFC-B4 브라켓 (SPFC-B4 BRACKET)</v>
+        <v>GKFC-B4 브라켓 (GKFC-B4 BRACKET)</v>
       </c>
       <c r="C18" t="str">
         <v>가공형 브라켓</v>
@@ -925,7 +925,7 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>SP-00055</v>
+        <v>GK-00055</v>
       </c>
       <c r="B19" t="str">
         <v>육각볼트 M6*L40_TAP10 (HEXAGON BOLT M6*L40_TAP10)</v>
@@ -954,7 +954,7 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>SP-00116</v>
+        <v>GK-00116</v>
       </c>
       <c r="B20" t="str">
         <v>육각볼트 M6*L42_TAP10 (HEXAGON BOLT M6*L42_TAP10)</v>
@@ -983,7 +983,7 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>SP-00051</v>
+        <v>GK-00051</v>
       </c>
       <c r="B21" t="str">
         <v>평와셔 M6*OD14*T1.5 (FLAT WASHER M6*OD14*T1.5)</v>
@@ -1012,7 +1012,7 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>SP-00117</v>
+        <v>GK-00117</v>
       </c>
       <c r="B22" t="str">
         <v>접지볼트 M5*L16 (STUD BOLT M5*L16)</v>
@@ -1041,7 +1041,7 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>SP-00118</v>
+        <v>GK-00118</v>
       </c>
       <c r="B23" t="str">
         <v>SUS 육각 너트 M5*OD8*L4 (SUS HEXAGON NUT M5*OD8*L4)</v>
@@ -1070,7 +1070,7 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>SP-00081</v>
+        <v>GK-00081</v>
       </c>
       <c r="B24" t="str">
         <v>평와셔 M5*OD12*T0.5 (FLAT WASHER M5*OD12*T0.5)</v>
@@ -1099,7 +1099,7 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>SP-00054</v>
+        <v>GK-00054</v>
       </c>
       <c r="B25" t="str">
         <v>트러스 볼트 M5*L35 (TRUSS BOLT M5*L35)</v>
@@ -1128,7 +1128,7 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>SP-00174</v>
+        <v>GK-00174</v>
       </c>
       <c r="B26" t="str">
         <v>트러스 볼트 M5*L43 (TRUSS BOLT M5*L43)</v>
@@ -1157,7 +1157,7 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>SP-00121</v>
+        <v>GK-00121</v>
       </c>
       <c r="B27" t="str">
         <v>2종 와셔붙이 볼트 M3*L10 (2 STAGE SEMS BOLT M3*L10)</v>
@@ -1186,7 +1186,7 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>SP-00122</v>
+        <v>GK-00122</v>
       </c>
       <c r="B28" t="str">
         <v>트러스 볼트 M5*L16 (TRUSS BOLT M5*L16)</v>
@@ -1215,7 +1215,7 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>SP-00011</v>
+        <v>GK-00011</v>
       </c>
       <c r="B29" t="str">
         <v>인서트 너트 M6*OD10*L10_Ni (INSERT NUT M6*OD10*L10_Ni)</v>
@@ -1244,7 +1244,7 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>SP-00123</v>
+        <v>GK-00123</v>
       </c>
       <c r="B30" t="str">
         <v>인서트 너트 M5*OD8*L10_Ni ( INSERT NUT M5*OD8*L10_Ni)</v>
@@ -1273,7 +1273,7 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>SP-00049</v>
+        <v>GK-00049</v>
       </c>
       <c r="B31" t="str">
         <v>T 복스 (T Handle Wrench)</v>
@@ -1302,10 +1302,10 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>SP-00124</v>
+        <v>GK-00124</v>
       </c>
       <c r="B32" t="str">
-        <v>SPFC-D1 가스켓 (SPFC-D1 GASKET)</v>
+        <v>GKFC-D1 가스켓 (GKFC-D1 GASKET)</v>
       </c>
       <c r="C32" t="str">
         <v/>
@@ -1331,10 +1331,10 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>SP-00175</v>
+        <v>GK-00175</v>
       </c>
       <c r="B33" t="str">
-        <v>SPFC-C1 인입구 그로멧 ID15-20 (SPFC-C1 CABLE GROMMET ID15-20)</v>
+        <v>GKFC-C1 인입구 그로멧 ID15-20 (GKFC-C1 CABLE GROMMET ID15-20)</v>
       </c>
       <c r="C33" t="str">
         <v>B-C1,C2,D1 (19,24,27) / 15-20mm</v>
@@ -1360,10 +1360,10 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>SP-00127</v>
+        <v>GK-00127</v>
       </c>
       <c r="B34" t="str">
-        <v>SPFC-D1 인입구 그로멧 ID23 (SPFC-D1 CABLE GROMMET ID23)</v>
+        <v>GKFC-D1 인입구 그로멧 ID23 (GKFC-D1 CABLE GROMMET ID23)</v>
       </c>
       <c r="C34" t="str">
         <v>B-D1 (27) / 23mm</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>SP-00146</v>
+        <v>GK-00146</v>
       </c>
       <c r="B35" t="str">
-        <v>PACKAGE BOX SPFC-D1 (FOR PRODUCT,NO PRINT)</v>
+        <v>PACKAGE BOX GKFC-D1 (FOR PRODUCT,NO PRINT)</v>
       </c>
       <c r="C35" t="str">
         <v>내측 : 625*315*205/NO PRINT</v>
@@ -1418,13 +1418,13 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>SP-00135</v>
+        <v>GK-00135</v>
       </c>
       <c r="B36" t="str">
         <v>트레이 선번 스티커 (Splice Tray KR L-24)</v>
       </c>
       <c r="C36" t="str">
-        <v>SPFC-C1/C2, ZOFC-D2</v>
+        <v>GKFC-C1/C2, ZOFC-D2</v>
       </c>
       <c r="D36" t="str">
         <v>1</v>
@@ -1447,13 +1447,13 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>SP-00172</v>
+        <v>GK-00172</v>
       </c>
       <c r="B37" t="str">
         <v>함체 상판 라벨 스티커</v>
       </c>
       <c r="C37" t="str">
-        <v>ZOFC-B1, ZOFC-D2 / SPFC-C1~ (124*44)</v>
+        <v>ZOFC-B1, ZOFC-D2 / GKFC-C1~ (124*44)</v>
       </c>
       <c r="D37" t="str">
         <v>1</v>
@@ -1476,10 +1476,10 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>SP-00131</v>
+        <v>GK-00131</v>
       </c>
       <c r="B38" t="str">
-        <v>SPFC-D1 트레이 커버 (SPFC-D1 TRAY COVER)</v>
+        <v>GKFC-D1 트레이 커버 (GKFC-D1 TRAY COVER)</v>
       </c>
       <c r="C38" t="str">
         <v/>
@@ -1505,7 +1505,7 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>SP-00132</v>
+        <v>GK-00132</v>
       </c>
       <c r="B39" t="str">
         <v>벨크로 L700 (Velcro Strap L700)</v>
@@ -1534,13 +1534,13 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>SP-00044</v>
+        <v>GK-00044</v>
       </c>
       <c r="B40" t="str">
         <v>진공 그리스(Grease)</v>
       </c>
       <c r="C40" t="str">
-        <v>5g, SPFC-B4, SPFC-B1, SPFC-B2</v>
+        <v>5g, GKFC-B4, GKFC-B1, GKFC-B2</v>
       </c>
       <c r="D40" t="str">
         <v>1</v>
@@ -1563,7 +1563,7 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>SP-00158</v>
+        <v>GK-00158</v>
       </c>
       <c r="B41" t="str">
         <v>보호튜브 ID8.2*OD10.2_무색_L600 (PROTECTION TUBE ID8.2*OD10.2_NC_L600)</v>
@@ -1592,7 +1592,7 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>SP-00042</v>
+        <v>GK-00042</v>
       </c>
       <c r="B42" t="str">
         <v>절연테이프 W19*L10000 (Insulation Tape W19*L10000)</v>
@@ -1621,7 +1621,7 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>SP-00004</v>
+        <v>GK-00004</v>
       </c>
       <c r="B43" t="str">
         <v>케이블 타이 L100 (CABLE TIE L100)</v>
@@ -1650,7 +1650,7 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>SP-00082</v>
+        <v>GK-00082</v>
       </c>
       <c r="B44" t="str">
         <v>케이블 타이 L200 (CABLE TIE L200)</v>
@@ -1679,7 +1679,7 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>SP-00008</v>
+        <v>GK-00008</v>
       </c>
       <c r="B45" t="str">
         <v>오링 P-5 (O-RING P-5)</v>
@@ -1708,7 +1708,7 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>SP-00047</v>
+        <v>GK-00047</v>
       </c>
       <c r="B46" t="str">
         <v>에어밸브 (AIR VALVE)</v>
@@ -1737,7 +1737,7 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>SP-00074</v>
+        <v>GK-00074</v>
       </c>
       <c r="B47" t="str">
         <v>지퍼백 W150*D200 (PLASTIC BAG W150*D200)</v>
@@ -1766,7 +1766,7 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>SP-00032</v>
+        <v>GK-00032</v>
       </c>
       <c r="B48" t="str">
         <v>지퍼백 W100*D150 (PLASTIC BAG W100*D150)</v>
@@ -1795,7 +1795,7 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>SP-00176</v>
+        <v>GK-00176</v>
       </c>
       <c r="B49" t="str">
         <v>지퍼백 W60*D80 (PLASTIC BAG W60*D80)</v>
@@ -1824,7 +1824,7 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>SP-00086</v>
+        <v>GK-00086</v>
       </c>
       <c r="B50" t="str">
         <v>지퍼백 W120*D250 (PLASTIC BAG W120*D250)</v>
@@ -1853,10 +1853,10 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>SP-00094</v>
+        <v>GK-00094</v>
       </c>
       <c r="B51" t="str">
-        <v>SPFC(B1,B2,B4,C1,C2,D1) MANUAL_250522</v>
+        <v>GKFC(B1,B2,B4,C1,C2,D1) MANUAL_250522</v>
       </c>
       <c r="C51" t="str">
         <v>영문 매뉴얼, 148.5*210mm</v>
@@ -1882,7 +1882,7 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>SP-00177</v>
+        <v>GK-00177</v>
       </c>
       <c r="B52" t="str">
         <v>RIBBON SPLICE PROTECTION SLEEVE (다심 열수축슬리브)</v>
@@ -1911,7 +1911,7 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>SP-00034</v>
+        <v>GK-00034</v>
       </c>
       <c r="B53" t="str">
         <v/>
@@ -1940,7 +1940,7 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>SP-00178</v>
+        <v>GK-00178</v>
       </c>
       <c r="B54" t="str">
         <v/>
